--- a/data/trans_orig/KIDM_A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_A_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>50833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59802</t>
+          <t>60428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65310</t>
+          <t>65312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113830</t>
+          <t>113423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120761</t>
+          <t>120154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91747</t>
+          <t>91296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96122</t>
+          <t>96120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85235</t>
+          <t>84798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90725</t>
+          <t>90721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179051</t>
+          <t>179542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186115</t>
+          <t>186160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52171</t>
+          <t>52201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>57124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111862</t>
+          <t>111892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,82 +1762,82 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6598</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>680</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5862</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69400</t>
+          <t>68664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152891</t>
+          <t>152686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158624</t>
+          <t>158626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>271214</t>
+          <t>272130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>280389</t>
+          <t>280393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>291820</t>
+          <t>290633</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299475</t>
+          <t>299655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>566540</t>
+          <t>567436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>578173</t>
+          <t>578572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>52320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62121</t>
+          <t>62245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67883</t>
+          <t>67865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116406</t>
+          <t>116884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124669</t>
+          <t>124718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83621</t>
+          <t>84060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>89529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81636</t>
+          <t>81538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168294</t>
+          <t>167863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176510</t>
+          <t>176514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56664</t>
+          <t>56842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>62042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121569</t>
+          <t>121820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126956</t>
+          <t>126957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74897</t>
+          <t>74702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81507</t>
+          <t>81496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80428</t>
+          <t>80363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86542</t>
+          <t>86543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158883</t>
+          <t>158740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166744</t>
+          <t>166685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276813</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287302</t>
+          <t>286730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>294289</t>
+          <t>294876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>305476</t>
+          <t>305092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>575732</t>
+          <t>576074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>590640</t>
+          <t>591012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>58688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65355</t>
+          <t>66077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121477</t>
+          <t>120941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128552</t>
+          <t>128555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92781</t>
+          <t>92867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>93655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188951</t>
+          <t>189206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194498</t>
+          <t>194520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58650</t>
+          <t>58161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64396</t>
+          <t>63260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124837</t>
+          <t>125261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>131903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94892</t>
+          <t>94852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90565</t>
+          <t>90598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187630</t>
+          <t>187934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>314949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>321914</t>
+          <t>322012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>314284</t>
+          <t>314754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>323553</t>
+          <t>323568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>633479</t>
+          <t>633860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>643740</t>
+          <t>644278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>27673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75945</t>
+          <t>75347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>842</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49634</t>
+          <t>50332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95630</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102014</t>
+          <t>102011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148802</t>
+          <t>148078</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155614</t>
+          <t>155568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70347</t>
+          <t>69738</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136239</t>
+          <t>136748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>49391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>51695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104122</t>
+          <t>104406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109689</t>
+          <t>109687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204751</t>
+          <t>204124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210620</t>
+          <t>210561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>264586</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>272001</t>
+          <t>271983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>472475</t>
+          <t>471831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>481608</t>
+          <t>481647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
